--- a/deliverables_to_zip/G090_Contribution.xlsx
+++ b/deliverables_to_zip/G090_Contribution.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lnd2kor\Desktop\ACI_Assignment2_group90\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lnd2kor\Desktop\PR_repo\ACI_Assignment2_group90\deliverables_to_zip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400AD2E1-B653-4C98-BE2B-EF3EBBDC6673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F2653D7-1FD7-4A4D-8839-AD2CA023FE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14100" yWindow="16080" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>BALAJI SEKHAR G</t>
   </si>
@@ -48,24 +48,6 @@
     <t>SAI NIKHIL KANDAGIRI</t>
   </si>
   <si>
-    <t>ANUSHA S</t>
-  </si>
-  <si>
-    <t>2025ab05110</t>
-  </si>
-  <si>
-    <t>2025aa05723</t>
-  </si>
-  <si>
-    <t>2025aa05579</t>
-  </si>
-  <si>
-    <t>2025aa05555</t>
-  </si>
-  <si>
-    <t>2025ab05074</t>
-  </si>
-  <si>
     <t>Student Registration Number</t>
   </si>
   <si>
@@ -73,6 +55,18 @@
   </si>
   <si>
     <t>Percentage of contribution out of 100%</t>
+  </si>
+  <si>
+    <t>2025AA05723</t>
+  </si>
+  <si>
+    <t>2025AA05555</t>
+  </si>
+  <si>
+    <t>2025AA05579</t>
+  </si>
+  <si>
+    <t>2025AB05110</t>
   </si>
 </sst>
 </file>
@@ -407,28 +401,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.85546875" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -439,7 +433,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -450,7 +444,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -467,17 +461,6 @@
         <v>3</v>
       </c>
       <c r="C5" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2">
         <v>1</v>
       </c>
     </row>
